--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8299-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8299-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95E917CE-5701-42F7-90C0-5E95247C87F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41EB7180-E1D8-429F-9132-96554CEE6116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{0669267A-B303-4984-80CD-00EAC23F55A8}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{FA851968-DB2E-4FC5-98B3-E3B36C86510B}"/>
   </bookViews>
   <sheets>
     <sheet name="8299-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1481,25 +1481,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EE57416-F6E4-400C-9DB3-8DD34B9C16F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7657A87F-AF35-4825-9DD0-51D1D934AB51}">
   <dimension ref="A1:R39"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1653,7 +1653,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="40">
         <v>2024</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2023</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2022</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2021</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2020</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2019</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2018</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2017</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2016</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2015</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2014</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2013</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2012</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2011</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2010</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2009</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2008</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2007</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2006</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2005</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2004</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2003</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2002</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
         <v>45</v>
       </c>
